--- a/pautas_excel/jueves 24 septiembre (corregido).xlsx
+++ b/pautas_excel/jueves 24 septiembre (corregido).xlsx
@@ -1511,7 +1511,7 @@
               <color rgb="00000000"/>
               <sz val="10.5"/>
             </rPr>
-            <t> </t>
+            <t xml:space="preserve"> </t>
           </r>
           <r>
             <rPr>
